--- a/data/PetRule.xlsx
+++ b/data/PetRule.xlsx
@@ -1,127 +1,122 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet name="PetRule" sheetId="1" state="visible" r:id="rId1"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PetRule" sheetId="1" r:id="R4a51648ca1804485"/>
+  </x:sheets>
+</x:workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-  </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
-</styleSheet>
+<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:fonts count="1">
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+  </x:fonts>
+  <x:fills count="2">
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+  </x:fills>
+  <x:borders count="1">
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+  </x:borders>
+  <x:cellStyleXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </x:cellStyleXfs>
+  <x:cellXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  </x:cellXfs>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0"/>
+  </x:cellStyles>
+  <x:colors>
+    <x:indexedColors>
+      <x:rgbColor rgb="00000000"/>
+      <x:rgbColor rgb="00FFFFFF"/>
+      <x:rgbColor rgb="00FF0000"/>
+      <x:rgbColor rgb="0000FF00"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00000000"/>
+      <x:rgbColor rgb="00FFFFFF"/>
+      <x:rgbColor rgb="00FF0000"/>
+      <x:rgbColor rgb="0000FF00"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00800000"/>
+      <x:rgbColor rgb="00008000"/>
+      <x:rgbColor rgb="00000080"/>
+      <x:rgbColor rgb="00808000"/>
+      <x:rgbColor rgb="00800080"/>
+      <x:rgbColor rgb="00008080"/>
+      <x:rgbColor rgb="00C0C0C0"/>
+      <x:rgbColor rgb="00808080"/>
+      <x:rgbColor rgb="009999FF"/>
+      <x:rgbColor rgb="00993366"/>
+      <x:rgbColor rgb="00FFFFCC"/>
+      <x:rgbColor rgb="00CCFFFF"/>
+      <x:rgbColor rgb="00660066"/>
+      <x:rgbColor rgb="00FF8080"/>
+      <x:rgbColor rgb="000066CC"/>
+      <x:rgbColor rgb="00CCCCFF"/>
+      <x:rgbColor rgb="00000080"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00800080"/>
+      <x:rgbColor rgb="00800000"/>
+      <x:rgbColor rgb="00008080"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="0000CCFF"/>
+      <x:rgbColor rgb="00CCFFFF"/>
+      <x:rgbColor rgb="00CCFFCC"/>
+      <x:rgbColor rgb="00FFFF99"/>
+      <x:rgbColor rgb="0099CCFF"/>
+      <x:rgbColor rgb="00FF99CC"/>
+      <x:rgbColor rgb="00CC99FF"/>
+      <x:rgbColor rgb="00FFCC99"/>
+      <x:rgbColor rgb="003366FF"/>
+      <x:rgbColor rgb="0033CCCC"/>
+      <x:rgbColor rgb="0099CC00"/>
+      <x:rgbColor rgb="00FFCC00"/>
+      <x:rgbColor rgb="00FF9900"/>
+      <x:rgbColor rgb="00FF6600"/>
+      <x:rgbColor rgb="00666699"/>
+      <x:rgbColor rgb="00969696"/>
+      <x:rgbColor rgb="00003366"/>
+      <x:rgbColor rgb="00339966"/>
+      <x:rgbColor rgb="00003300"/>
+      <x:rgbColor rgb="00333300"/>
+      <x:rgbColor rgb="00993300"/>
+      <x:rgbColor rgb="00993366"/>
+      <x:rgbColor rgb="00333399"/>
+      <x:rgbColor rgb="00333333"/>
+    </x:indexedColors>
+  </x:colors>
+</x:styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -288,7 +283,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -297,13 +292,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -337,17 +332,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -402,107 +386,100 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>max_pets</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>name_max_len</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>rename_cost_gold</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>summon_cooldown_seconds</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>desc</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>规则行 id(固定 1)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>可携带宝宝数量上限</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>宝宝名最大长度(UTF-8 码点数)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>改名金币(0=免费)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>召唤/收回冷却秒(0=无冷却)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" t="n">
-        <v>10</v>
-      </c>
-      <c r="C6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>200</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>宝宝系统全局规则(单行)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">max_pets</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">name_max_len</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">rename_cost_gold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">summon_cooldown_seconds</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">desc</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">规则行 id(固定 1)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">可携带宝宝数量上限</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">宝宝名最大长度(UTF-8 码点数)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">改名金币(0=免费)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">召唤/收回冷却秒(0=无冷却)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">说明</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="E6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">宝宝系统全局规则(单行)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>